--- a/artfynd/A 57865-2025 artfynd.xlsx
+++ b/artfynd/A 57865-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404281</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404269</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404278</v>
       </c>
       <c r="B4" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404279</v>
       </c>
       <c r="B5" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137404270</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>137404261</v>
       </c>
       <c r="B23" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>137404265</v>
       </c>
       <c r="B24" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137404271</v>
       </c>
       <c r="B25" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57865-2025 artfynd.xlsx
+++ b/artfynd/A 57865-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404281</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404269</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404278</v>
       </c>
       <c r="B4" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404279</v>
       </c>
       <c r="B5" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137404270</v>
       </c>
       <c r="B22" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>137404261</v>
       </c>
       <c r="B23" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>137404265</v>
       </c>
       <c r="B24" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137404271</v>
       </c>
       <c r="B25" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57865-2025 artfynd.xlsx
+++ b/artfynd/A 57865-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404281</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404269</v>
       </c>
       <c r="B3" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404278</v>
       </c>
       <c r="B4" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404279</v>
       </c>
       <c r="B5" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137404284</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137404254</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137404262</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137404263</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137404264</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>137404267</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137404272</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137404273</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137404274</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>137404275</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>137404276</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>137404280</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137404283</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>137404286</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>137404255</v>
       </c>
       <c r="B20" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137404256</v>
       </c>
       <c r="B21" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137404270</v>
       </c>
       <c r="B22" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>137404261</v>
       </c>
       <c r="B23" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>137404265</v>
       </c>
       <c r="B24" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137404271</v>
       </c>
       <c r="B25" t="n">
-        <v>80429</v>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
